--- a/Maruti_Comps_.xlsx
+++ b/Maruti_Comps_.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hrida\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88161E26-ED2A-4799-8104-DF9AA1447E91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5EC6F17-D2A3-43B9-B659-316B005C0C22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -179,33 +179,33 @@
       <b/>
       <sz val="13"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF666666"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -273,10 +273,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -295,6 +293,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -574,259 +575,260 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
     </row>
     <row r="4" spans="1:6" ht="28.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="10">
         <v>13520</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="10">
         <v>475</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="10">
         <v>3418</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="10">
         <v>2018.6</v>
       </c>
-      <c r="F5" s="4"/>
+      <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="11">
         <v>314.39999999999998</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="10">
         <v>3705</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="10">
         <v>1201</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="10">
         <v>812.5</v>
       </c>
-      <c r="F6" s="4"/>
+      <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="4">
         <f>B5*B6</f>
         <v>4250688</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="4">
         <f>C5*C6</f>
         <v>1759875</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="4">
         <f>D5*D6</f>
         <v>4105018</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="4">
         <f>E5*E6</f>
         <v>1640112.5</v>
       </c>
-      <c r="F7" s="4"/>
+      <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="10">
         <v>-55000</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="10">
         <v>1080000</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="10">
         <v>500000</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="10">
         <v>-100000</v>
       </c>
-      <c r="F8" s="4"/>
+      <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="4">
         <f>B7+B8</f>
         <v>4195688</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="4">
         <f>C7+C8</f>
         <v>2839875</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="4">
         <f>D7+D8</f>
         <v>4605018</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="4">
         <f>E7+E8</f>
         <v>1540112.5</v>
       </c>
-      <c r="F9" s="4"/>
+      <c r="F9" s="2"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="10">
         <v>214502</v>
       </c>
-      <c r="C10" s="12">
-        <v>466390</v>
-      </c>
-      <c r="D10" s="12">
+      <c r="C10" s="10">
+        <v>87410</v>
+      </c>
+      <c r="D10" s="10">
         <v>230000</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="10">
         <v>89410</v>
       </c>
-      <c r="F10" s="4"/>
+      <c r="F10" s="2"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="10">
         <v>459</v>
       </c>
-      <c r="C11" s="12">
-        <v>78.8</v>
-      </c>
-      <c r="D11" s="12">
+      <c r="C11" s="10">
+        <v>8.23</v>
+      </c>
+      <c r="D11" s="10">
         <v>124.7</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="10">
         <v>69.400000000000006</v>
       </c>
-      <c r="F11" s="4"/>
+      <c r="F11" s="2"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="5">
         <f>IFERROR(B5/B11,"-")</f>
         <v>29.455337690631808</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="5">
         <f>IFERROR(C5/C11,"-")</f>
-        <v>6.0279187817258881</v>
-      </c>
-      <c r="D12" s="7">
+        <v>57.715674362089914</v>
+      </c>
+      <c r="D12" s="5">
         <f>IFERROR(D5/D11,"-")</f>
         <v>27.409783480352846</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="5">
         <f>IFERROR(E5/E11,"-")</f>
         <v>29.0864553314121</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="5">
         <f>IFERROR(AVERAGE(C12:E12),"-")</f>
-        <v>20.841385864496946</v>
+        <v>38.070637724618287</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="5">
         <f>IFERROR(B9/B10,"-")</f>
         <v>19.56013463743928</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="5">
         <f>IFERROR(C9/C10,"-")</f>
-        <v>6.0890563691331288</v>
-      </c>
-      <c r="D13" s="7">
+        <v>32.489131678297674</v>
+      </c>
+      <c r="D13" s="5">
         <f>IFERROR(D9/D10,"-")</f>
         <v>20.021817391304349</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="5">
         <f>IFERROR(E9/E10,"-")</f>
         <v>17.225282406889608</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="5">
         <f>IFERROR(AVERAGE(C13:E13),"-")</f>
-        <v>14.445385389109029</v>
+        <v>23.245410492163874</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="9">
+      <c r="B18" s="7">
         <f>IFERROR(F12*B11,"-")</f>
-        <v>9566.1961118040981</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
+        <v>17474.422715599794</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="9">
+      <c r="B19" s="7">
         <f>IFERROR((F13*B10-B8)/B6,"-")</f>
-        <v>10030.420027782013</v>
-      </c>
+        <v>16034.309928085671</v>
+      </c>
+      <c r="C19" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -848,47 +850,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="9" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="9" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="9" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="9" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="9" t="s">
         <v>37</v>
       </c>
     </row>
@@ -917,7 +919,7 @@
       <c r="A12" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="12" t="s">
         <v>33</v>
       </c>
     </row>
